--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>1376</v>
+        <v>1274</v>
       </c>
       <c r="D2" t="n">
-        <v>620</v>
+        <v>725</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C3" t="n">
-        <v>805</v>
+        <v>599</v>
       </c>
       <c r="D3" t="n">
-        <v>2938</v>
+        <v>3401</v>
       </c>
       <c r="E3" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>2181</v>
+        <v>1873</v>
       </c>
       <c r="D5" t="n">
-        <v>4109</v>
+        <v>4126</v>
       </c>
       <c r="E5" t="n">
-        <v>710</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
